--- a/samples/turnos_ejemplo.xlsx
+++ b/samples/turnos_ejemplo.xlsx
@@ -508,7 +508,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="4">
-        <x:v>46307</x:v>
+        <x:v>46672</x:v>
       </x:c>
       <x:c r="C2" s="5">
         <x:v>0.333333333333333</x:v>
@@ -525,7 +525,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="4">
-        <x:v>46307</x:v>
+        <x:v>46672</x:v>
       </x:c>
       <x:c r="C3" s="5">
         <x:v>0.583333333333333</x:v>
@@ -542,7 +542,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="4">
-        <x:v>46307</x:v>
+        <x:v>46672</x:v>
       </x:c>
       <x:c r="C4" s="5">
         <x:v>0.916666666666667</x:v>
@@ -559,7 +559,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="4">
-        <x:v>46307</x:v>
+        <x:v>46672</x:v>
       </x:c>
       <x:c r="C5" s="5">
         <x:v>0.375</x:v>
@@ -576,7 +576,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="4">
-        <x:v>46307</x:v>
+        <x:v>46672</x:v>
       </x:c>
       <x:c r="C6" s="5">
         <x:v>0.291666666666667</x:v>
@@ -593,7 +593,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="4">
-        <x:v>46308</x:v>
+        <x:v>46673</x:v>
       </x:c>
       <x:c r="C7" s="5">
         <x:v>0.916666666666667</x:v>
@@ -610,7 +610,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="4">
-        <x:v>46308</x:v>
+        <x:v>46673</x:v>
       </x:c>
       <x:c r="C8" s="5">
         <x:v>0.333333333333333</x:v>
@@ -627,7 +627,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="4">
-        <x:v>46308</x:v>
+        <x:v>46673</x:v>
       </x:c>
       <x:c r="C9" s="5">
         <x:v>0.5</x:v>
@@ -644,7 +644,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="4">
-        <x:v>46309</x:v>
+        <x:v>46674</x:v>
       </x:c>
       <x:c r="C10" s="5">
         <x:v>0.25</x:v>
